--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487054_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487054_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1448</v>
+        <v>4.9376</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2451</v>
+        <v>3.904</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8997000000000001</v>
+        <v>1.0336</v>
       </c>
       <c r="G2" t="n">
         <v>3.6548</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>0.355</v>
+        <v>0.1477</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2049</v>
+        <v>-0.1361</v>
       </c>
       <c r="U2" t="n">
-        <v>0.15</v>
+        <v>0.2839</v>
       </c>
       <c r="V2" t="n">
         <v>0.9421</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3688</v>
+        <v>0.9613</v>
       </c>
       <c r="E3" t="n">
-        <v>2.366</v>
+        <v>1.8247</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9973</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>-1.3795</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.355</v>
+        <v>-0.0525</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6359</v>
+        <v>0.0945</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2809</v>
+        <v>-0.1471</v>
       </c>
       <c r="V3" t="n">
         <v>0.6562</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4509</v>
+        <v>0.5243</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4149</v>
+        <v>-0.0294</v>
       </c>
       <c r="F4" t="n">
-        <v>0.036</v>
+        <v>0.5536</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5419</v>
+        <v>0.6212</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3178</v>
+        <v>0.4306</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8597</v>
+        <v>0.1906</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7123</v>
+        <v>1.2953</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7452</v>
+        <v>1.0918</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0328</v>
+        <v>0.2035</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2542</v>
+        <v>-0.6741</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4274</v>
+        <v>-0.6612</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8268</v>
+        <v>-0.0129</v>
       </c>
       <c r="P4" t="n">
-        <v>0.772</v>
+        <v>-0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>0.772</v>
+        <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2208</v>
+        <v>-0.1742</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2974</v>
+        <v>-0.2945</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5182</v>
+        <v>0.1203</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0498</v>
+        <v>0.4499</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3893</v>
+        <v>0.5745</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3395</v>
+        <v>-0.1246</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6212</v>
+        <v>-0.5419</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4306</v>
+        <v>0.3178</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1906</v>
+        <v>-0.8597</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2953</v>
+        <v>0.7123</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0918</v>
+        <v>0.7452</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2035</v>
+        <v>-0.0328</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6741</v>
+        <v>-1.2542</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6612</v>
+        <v>-0.4274</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0129</v>
+        <v>-0.8268</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7482</v>
+        <v>0.2198</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6544</v>
+        <v>-0.1378</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0939</v>
+        <v>0.3576</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6562</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.3872</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0507</v>
+        <v>0.1089</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5496</v>
+        <v>-0.4961</v>
       </c>
       <c r="G6" t="n">
         <v>0.4176</v>
@@ -922,13 +922,13 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8249</v>
+        <v>-0.6118</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2234</v>
+        <v>-0.0638</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6015</v>
+        <v>-0.548</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9949</v>
+        <v>-0.9414</v>
       </c>
       <c r="E7" t="n">
         <v>-0.8836000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1112</v>
+        <v>-0.0577</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0655</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1589</v>
+        <v>-1.1609</v>
       </c>
       <c r="E8" t="n">
-        <v>0.016</v>
+        <v>0.3353</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.175</v>
+        <v>-1.4962</v>
       </c>
       <c r="G8" t="n">
         <v>1.1598</v>
@@ -1078,13 +1078,13 @@
         <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5394</v>
+        <v>-0.5414</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5803</v>
+        <v>-0.2611</v>
       </c>
       <c r="U8" t="n">
-        <v>0.041</v>
+        <v>-0.2803</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0422</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5945</v>
+        <v>-1.8087</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2623</v>
+        <v>-1.5032</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3322</v>
+        <v>-0.3055</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1015</v>
@@ -1156,13 +1156,13 @@
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.265</v>
+        <v>-0.4792</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0462</v>
+        <v>-0.2872</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2188</v>
+        <v>-0.192</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5527</v>
+        <v>-1.8923</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0905</v>
+        <v>-0.4302</v>
       </c>
       <c r="F10" t="n">
         <v>-1.4621</v>
@@ -1234,10 +1234,10 @@
         <v>1.9301</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.1566</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3087</v>
+        <v>-0.6484</v>
       </c>
       <c r="U10" t="n">
         <v>0.4918</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7824</v>
+        <v>-2.7182</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4635</v>
+        <v>-0.572</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3189</v>
+        <v>-2.1462</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.463</v>
+        <v>0.1099</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1014</v>
+        <v>2.2769</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3616</v>
+        <v>-2.167</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.86</v>
+        <v>2.3519</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2331</v>
+        <v>3.0116</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6269</v>
+        <v>-0.6597</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6029</v>
+        <v>-2.242</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8682</v>
+        <v>-0.7347</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.7347</v>
+        <v>-1.5073</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5091</v>
+        <v>-0.386</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R11" t="n">
         <v>2.5091</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5004</v>
+        <v>-0.272</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1752</v>
+        <v>-0.6005</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6748</v>
+        <v>0.3285</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3281</v>
+        <v>-2.1701</v>
       </c>
       <c r="W11" t="n">
         <v>0.5717</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.8999</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0979</v>
+        <v>-2.8121</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7911</v>
+        <v>-0.9846</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3068</v>
+        <v>-1.8275</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1099</v>
+        <v>-4.463</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2769</v>
+        <v>-1.1014</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.167</v>
+        <v>-3.3616</v>
       </c>
       <c r="J12" t="n">
-        <v>2.3519</v>
+        <v>-0.86</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0116</v>
+        <v>-0.2331</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6597</v>
+        <v>-0.6269</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.242</v>
+        <v>-3.6029</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7347</v>
+        <v>-0.8682</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5073</v>
+        <v>-2.7347</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.386</v>
+        <v>2.5091</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.5301</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8196</v>
+        <v>-0.6963</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1679</v>
+        <v>0.1662</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1701</v>
+        <v>-0.3281</v>
       </c>
       <c r="W12" t="n">
         <v>0.5717</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7418</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4376</v>
+        <v>-3.5645</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8556</v>
+        <v>-1.1967</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.582</v>
+        <v>-2.3678</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6094</v>
@@ -1468,13 +1468,13 @@
         <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4072</v>
+        <v>-0.5341</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3847</v>
+        <v>0.0436</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7919</v>
+        <v>-0.5777</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.304500000000001</v>
+        <v>-8.4122</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2554000000000002</v>
+        <v>1.147699999999999</v>
       </c>
       <c r="F14" t="n">
         <v>-9.559899999999999</v>
@@ -1516,7 +1516,7 @@
         <v>2.871800000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.507099999999999</v>
+        <v>-9.507100000000001</v>
       </c>
       <c r="J14" t="n">
         <v>11.9801</v>
@@ -1537,7 +1537,7 @@
         <v>-11.703</v>
       </c>
       <c r="P14" t="n">
-        <v>3.860199999999999</v>
+        <v>3.8602</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.5454</v>
@@ -1546,13 +1546,13 @@
         <v>16.4056</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.7873</v>
+        <v>-2.8952</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.8797</v>
+        <v>-2.9876</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09239999999999982</v>
+        <v>0.09240000000000004</v>
       </c>
       <c r="V14" t="n">
         <v>-2.7419</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1261</v>
+        <v>3.7381</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0741</v>
+        <v>1.8738</v>
       </c>
       <c r="F15" t="n">
-        <v>2.052</v>
+        <v>1.8642</v>
       </c>
       <c r="G15" t="n">
         <v>-1.803</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6432</v>
+        <v>1.2552</v>
       </c>
       <c r="T15" t="n">
-        <v>0.234</v>
+        <v>0.0338</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4092</v>
+        <v>1.2215</v>
       </c>
       <c r="V15" t="n">
         <v>2.7418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>E. AMANDIO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9768</v>
+        <v>2.7035</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6574</v>
+        <v>2.4973</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3193</v>
+        <v>0.2062</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3705</v>
+        <v>6.0616</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2495</v>
+        <v>2.6186</v>
       </c>
       <c r="I16" t="n">
-        <v>3.121</v>
+        <v>3.443</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4306</v>
+        <v>8.177099999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7038</v>
+        <v>4.295</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7268</v>
+        <v>3.8822</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0601</v>
+        <v>-2.1156</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4542</v>
+        <v>-1.6764</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3941</v>
+        <v>-0.4391</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9301</v>
+        <v>-4.2462</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8951</v>
+        <v>-6.7553</v>
       </c>
       <c r="R16" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2083</v>
+        <v>0.9726</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1639</v>
+        <v>-0.0257</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3722</v>
+        <v>0.9984</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3281</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2859</v>
+        <v>1.1012</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0422</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. AMANDIO</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.69</v>
+        <v>2.5346</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6976</v>
+        <v>0.8577</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0076</v>
+        <v>1.6769</v>
       </c>
       <c r="G17" t="n">
-        <v>6.0616</v>
+        <v>3.3705</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6186</v>
+        <v>0.2495</v>
       </c>
       <c r="I17" t="n">
-        <v>3.443</v>
+        <v>3.121</v>
       </c>
       <c r="J17" t="n">
-        <v>8.177099999999999</v>
+        <v>3.4306</v>
       </c>
       <c r="K17" t="n">
-        <v>4.295</v>
+        <v>0.7038</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8822</v>
+        <v>2.7268</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1156</v>
+        <v>-0.0601</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6764</v>
+        <v>-0.4542</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4391</v>
+        <v>0.3941</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.2462</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.7553</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5091</v>
+        <v>0.965</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9591</v>
+        <v>0.7661</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1745</v>
+        <v>0.0364</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7845</v>
+        <v>0.7297</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.3281</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1012</v>
+        <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1857</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4688</v>
+        <v>2.1844</v>
       </c>
       <c r="E18" t="n">
-        <v>1.607</v>
+        <v>1.7072</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1382</v>
+        <v>0.4772</v>
       </c>
       <c r="G18" t="n">
         <v>1.7484</v>
@@ -1858,13 +1858,13 @@
         <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2446</v>
+        <v>0.471</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1507</v>
+        <v>-0.0505</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0939</v>
+        <v>0.5215</v>
       </c>
       <c r="V18" t="n">
         <v>-0.614</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8026</v>
+        <v>1.1774</v>
       </c>
       <c r="E19" t="n">
         <v>3.3879</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5853</v>
+        <v>-2.2106</v>
       </c>
       <c r="G19" t="n">
         <v>1.2995</v>
@@ -1936,13 +1936,13 @@
         <v>1.3511</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5089</v>
+        <v>-0.1342</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3146</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1943</v>
+        <v>0.1804</v>
       </c>
       <c r="V19" t="n">
         <v>1.5561</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FRECHILLA GOMEZ</t>
+          <t>D. IBARLUCEA LAVIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5331</v>
+        <v>-0.5245</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1972</v>
+        <v>-0.6439</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7302999999999999</v>
+        <v>0.1193</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5151</v>
+        <v>-2.4928</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5837</v>
+        <v>-2.2157</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.277</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8266</v>
+        <v>-0.5107</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7452</v>
+        <v>-0.6728</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0814</v>
+        <v>0.1621</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3417</v>
+        <v>-1.982</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3288</v>
+        <v>-1.5429</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0129</v>
+        <v>-0.4391</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2908</v>
+        <v>0.6871</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0727</v>
+        <v>-0.1331</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2181</v>
+        <v>0.8202</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
       <c r="W20" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. IBARLUCEA LAVIN</t>
+          <t>A. FRECHILLA GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.012</v>
+        <v>-0.5867</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9443</v>
+        <v>0.1972</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0677</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4928</v>
+        <v>-0.5151</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2157</v>
+        <v>-0.5837</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.277</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5107</v>
+        <v>0.8266</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6728</v>
+        <v>0.7452</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1621</v>
+        <v>0.0814</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.982</v>
+        <v>-1.3417</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5429</v>
+        <v>-1.3288</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4391</v>
+        <v>-0.0129</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5091</v>
+        <v>-0.965</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5091</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1996</v>
+        <v>0.2373</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4336</v>
+        <v>0.0727</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6332</v>
+        <v>0.1646</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.228</v>
+        <v>0.6562</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2146</v>
+        <v>-1.2546</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1171</v>
+        <v>-0.3173</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0976</v>
+        <v>-0.9373</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0336</v>
@@ -2170,13 +2170,13 @@
         <v>0.193</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2399</v>
+        <v>0.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4891</v>
+        <v>0.2889</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2492</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.614</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.304600000000001</v>
+        <v>9.972200000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>9.559799999999999</v>
+        <v>9.559900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2554000000000007</v>
+        <v>0.4121000000000006</v>
       </c>
       <c r="G23" t="n">
-        <v>6.635500000000002</v>
+        <v>6.635500000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-2.8717</v>
@@ -2224,7 +2224,7 @@
         <v>18.6156</v>
       </c>
       <c r="K23" t="n">
-        <v>6.912699999999999</v>
+        <v>6.912700000000001</v>
       </c>
       <c r="L23" t="n">
         <v>11.7029</v>
@@ -2239,7 +2239,7 @@
         <v>-2.1956</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.8602</v>
+        <v>-3.860199999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.4056</v>
@@ -2248,16 +2248,16 @@
         <v>12.5455</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7874</v>
+        <v>4.4551</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0925</v>
+        <v>-0.09210000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>3.8798</v>
+        <v>4.5474</v>
       </c>
       <c r="V23" t="n">
-        <v>2.7417</v>
+        <v>2.741700000000001</v>
       </c>
       <c r="W23" t="n">
         <v>7.442500000000001</v>
